--- a/research/traditional_assets/database/data/mauritius/mauritius_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ9"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.23015</v>
+        <v>0.0165</v>
       </c>
       <c r="E2">
-        <v>0.06249999999999999</v>
+        <v>0.358</v>
       </c>
       <c r="G2">
-        <v>0.05440534521158129</v>
+        <v>0.0581453634085213</v>
       </c>
       <c r="H2">
-        <v>0.05440534521158129</v>
+        <v>0.0581453634085213</v>
       </c>
       <c r="I2">
-        <v>0.8675278396436525</v>
+        <v>0.7575313283208021</v>
       </c>
       <c r="J2">
-        <v>0.8048338007018965</v>
+        <v>0.7514094983927589</v>
       </c>
       <c r="K2">
-        <v>98.345</v>
+        <v>117.422</v>
       </c>
       <c r="L2">
-        <v>0.8761247216035635</v>
+        <v>0.7357268170426066</v>
       </c>
       <c r="M2">
-        <v>4.47</v>
+        <v>6.92048</v>
       </c>
       <c r="N2">
-        <v>0.005377831783346767</v>
+        <v>0.006494444444444445</v>
       </c>
       <c r="O2">
-        <v>0.04545223448065484</v>
+        <v>0.05893682614842194</v>
       </c>
       <c r="P2">
-        <v>4.47</v>
+        <v>6.92048</v>
       </c>
       <c r="Q2">
-        <v>0.005377831783346767</v>
+        <v>0.006494444444444445</v>
       </c>
       <c r="R2">
-        <v>0.04545223448065484</v>
+        <v>0.05893682614842194</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11.227</v>
+        <v>12.272</v>
       </c>
       <c r="V2">
-        <v>0.01350714036501883</v>
+        <v>0.01151651651651652</v>
       </c>
       <c r="W2">
-        <v>0.1110147441457068</v>
+        <v>0.05284552845528456</v>
       </c>
       <c r="X2">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="Y2">
-        <v>0.0536007502411757</v>
+        <v>-0.04119481426690733</v>
       </c>
       <c r="Z2">
-        <v>0.1011028087215921</v>
+        <v>0.06194322414481673</v>
       </c>
       <c r="AA2">
-        <v>0.1148800645031244</v>
+        <v>0.03097623653740652</v>
       </c>
       <c r="AB2">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AC2">
-        <v>0.05746607059859322</v>
+        <v>-0.06632220898098112</v>
       </c>
       <c r="AD2">
-        <v>54.23</v>
+        <v>228.73</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>54.23</v>
+        <v>228.73</v>
       </c>
       <c r="AG2">
-        <v>43.003</v>
+        <v>216.458</v>
       </c>
       <c r="AH2">
-        <v>0.06124776942016218</v>
+        <v>0.1767169114522572</v>
       </c>
       <c r="AI2">
-        <v>0.03727070919499942</v>
+        <v>0.1021267893843147</v>
       </c>
       <c r="AJ2">
-        <v>0.04919165447446959</v>
+        <v>0.1688363552974982</v>
       </c>
       <c r="AK2">
-        <v>0.02978453431666232</v>
+        <v>0.09717988951218801</v>
       </c>
       <c r="AL2">
-        <v>2.573</v>
+        <v>18.275</v>
       </c>
       <c r="AM2">
-        <v>2.496</v>
+        <v>18.098</v>
       </c>
       <c r="AN2">
-        <v>17</v>
+        <v>29.7051948051948</v>
       </c>
       <c r="AO2">
-        <v>37.84687135639332</v>
+        <v>6.615704514363886</v>
       </c>
       <c r="AP2">
-        <v>13.48056426332288</v>
+        <v>28.11142857142857</v>
       </c>
       <c r="AQ2">
-        <v>39.01442307692307</v>
+        <v>6.680406674770693</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tadvest Limited (NMSE:TAD)</t>
+          <t>National Investment Trust Ltd (MUSE:NITL.N0000)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,76 +722,79 @@
         </is>
       </c>
       <c r="D3">
-        <v>1.847</v>
+        <v>0.522</v>
       </c>
       <c r="E3">
-        <v>0.401</v>
+        <v>0.736</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.9329962073324904</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.9329962073324904</v>
       </c>
       <c r="I3">
-        <v>0.9760479041916168</v>
+        <v>0.9683944374209861</v>
       </c>
       <c r="J3">
-        <v>0.9760479041916168</v>
+        <v>0.9683944374209861</v>
       </c>
       <c r="K3">
-        <v>15.3</v>
+        <v>7.18</v>
       </c>
       <c r="L3">
-        <v>0.9161676646706588</v>
+        <v>0.9077117572692793</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.419</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.02193717277486911</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.05835654596100279</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.419</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02193717277486911</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.05835654596100279</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>0.437</v>
+        <v>4.13</v>
       </c>
       <c r="V3">
-        <v>0.01076354679802956</v>
+        <v>0.2162303664921466</v>
       </c>
       <c r="W3">
-        <v>0.3097165991902834</v>
+        <v>0.2484429065743945</v>
       </c>
       <c r="X3">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="Y3">
-        <v>0.2523026052857523</v>
+        <v>0.1544025638522026</v>
       </c>
       <c r="Z3">
-        <v>0.3423464053627437</v>
+        <v>0.3110499410145497</v>
       </c>
       <c r="AA3">
-        <v>0.3341464914618397</v>
+        <v>0.3012190326386158</v>
       </c>
       <c r="AB3">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AC3">
-        <v>0.2767324975573085</v>
+        <v>0.2071786899164239</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.437</v>
+        <v>-4.13</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,22 +815,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.01088066130518139</v>
+        <v>-0.2758851035404141</v>
       </c>
       <c r="AK3">
-        <v>-0.006789615151562233</v>
+        <v>-0.1737484223811527</v>
       </c>
       <c r="AL3">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.055</v>
-      </c>
-      <c r="AO3">
-        <v>740.909090909091</v>
-      </c>
-      <c r="AQ3">
-        <v>-296.3636363636364</v>
+        <v>0</v>
+      </c>
+      <c r="AN3">
+        <v>0</v>
+      </c>
+      <c r="AP3">
+        <v>-0.5363636363636364</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Mauritius Development Investment Trust Company Limited (MUSE:MDIT.N0000)</t>
+          <t>EPE Capital Partners Ltd (JSE:EPE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -846,6 +849,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>0.31</v>
+      </c>
+      <c r="E4">
+        <v>0.358</v>
+      </c>
       <c r="G4">
         <v>0</v>
       </c>
@@ -853,16 +862,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.951923076923077</v>
+        <v>0.9839743589743589</v>
       </c>
       <c r="J4">
-        <v>0.9512820512820513</v>
+        <v>0.9776415136190223</v>
       </c>
       <c r="K4">
-        <v>8.91</v>
+        <v>28.7</v>
       </c>
       <c r="L4">
-        <v>0.951923076923077</v>
+        <v>0.9198717948717948</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -886,61 +895,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.597</v>
+        <v>0.19</v>
       </c>
       <c r="V4">
-        <v>0.02072916666666667</v>
+        <v>0.002219626168224299</v>
       </c>
       <c r="W4">
-        <v>0.3337078651685393</v>
+        <v>0.2385702410640066</v>
       </c>
       <c r="X4">
-        <v>0.06019893055196306</v>
+        <v>0.1094540762025605</v>
       </c>
       <c r="Y4">
-        <v>0.2735089346165763</v>
+        <v>0.1291161648614461</v>
       </c>
       <c r="Z4">
-        <v>0.31033453797951</v>
+        <v>0.2383881294936545</v>
       </c>
       <c r="AA4">
-        <v>0.2952156758728159</v>
+        <v>0.2330581317469838</v>
       </c>
       <c r="AB4">
-        <v>0.05828818886448089</v>
+        <v>0.09798895501806384</v>
       </c>
       <c r="AC4">
-        <v>0.236927487008335</v>
+        <v>0.13506917672892</v>
       </c>
       <c r="AD4">
-        <v>2.23</v>
+        <v>28.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.23</v>
+        <v>28.1</v>
       </c>
       <c r="AG4">
-        <v>1.633</v>
+        <v>27.91</v>
       </c>
       <c r="AH4">
-        <v>0.07186593619078312</v>
+        <v>0.247141600703606</v>
       </c>
       <c r="AI4">
-        <v>0.06329832529094523</v>
+        <v>0.173778602350031</v>
       </c>
       <c r="AJ4">
-        <v>0.05365885716163375</v>
+        <v>0.2458814201391948</v>
       </c>
       <c r="AK4">
-        <v>0.04715156065024687</v>
+        <v>0.1728066373599158</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>1.53</v>
+      </c>
+      <c r="AO4">
+        <v>20.06535947712418</v>
+      </c>
+      <c r="AQ4">
+        <v>20.06535947712418</v>
       </c>
     </row>
     <row r="5">
@@ -960,46 +975,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.08</v>
+        <v>-0.0629</v>
       </c>
       <c r="E5">
-        <v>-0.327</v>
+        <v>-0.0071</v>
       </c>
       <c r="G5">
-        <v>0.6124183006535948</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>0.6124183006535948</v>
+        <v>0</v>
       </c>
       <c r="I5">
-        <v>0.8235294117647058</v>
+        <v>0.7791411042944786</v>
       </c>
       <c r="J5">
-        <v>0.8222426470588234</v>
+        <v>0.7773291482379797</v>
       </c>
       <c r="K5">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="L5">
-        <v>0.8300653594771242</v>
+        <v>0.7914110429447854</v>
       </c>
       <c r="M5">
-        <v>0.1764</v>
+        <v>0.96138</v>
       </c>
       <c r="N5">
-        <v>0.03046632124352332</v>
+        <v>0.0882</v>
       </c>
       <c r="O5">
-        <v>0.1388976377952756</v>
+        <v>0.7452558139534884</v>
       </c>
       <c r="P5">
-        <v>0.1764</v>
+        <v>0.96138</v>
       </c>
       <c r="Q5">
-        <v>0.03046632124352332</v>
+        <v>0.0882</v>
       </c>
       <c r="R5">
-        <v>0.1388976377952756</v>
+        <v>0.7452558139534884</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1008,31 +1023,31 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>5.18</v>
+        <v>5.82</v>
       </c>
       <c r="V5">
-        <v>0.8946459412780656</v>
+        <v>0.5339449541284403</v>
       </c>
       <c r="W5">
-        <v>0.09844961240310078</v>
+        <v>0.09923076923076923</v>
       </c>
       <c r="X5">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="Y5">
-        <v>0.04103561849856963</v>
+        <v>0.005190426508577345</v>
       </c>
       <c r="Z5">
-        <v>0.1514851485148515</v>
+        <v>0.2084398976982097</v>
       </c>
       <c r="AA5">
-        <v>0.1245575495049505</v>
+        <v>0.162026408136561</v>
       </c>
       <c r="AB5">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AC5">
-        <v>0.06714355560041932</v>
+        <v>0.06798606541436908</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1044,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-5.18</v>
+        <v>-5.82</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1053,10 +1068,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-8.49180327868852</v>
+        <v>-1.145669291338583</v>
       </c>
       <c r="AK5">
-        <v>-0.6624040920716112</v>
+        <v>-0.8584070796460178</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1073,7 +1088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Investment Trust Ltd (MUSE:NITL.N0000)</t>
+          <t>African Rainbow Capital Investments Limited (JSE:AIL)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1081,80 +1096,71 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>0.448</v>
-      </c>
-      <c r="E6">
-        <v>0.366</v>
-      </c>
       <c r="G6">
-        <v>0.8919597989949748</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>0.8919597989949748</v>
+        <v>0</v>
       </c>
       <c r="I6">
-        <v>0.7839195979899498</v>
+        <v>0.8270980788675429</v>
       </c>
       <c r="J6">
-        <v>0.7810689812699864</v>
+        <v>0.8270980788675429</v>
       </c>
       <c r="K6">
-        <v>3.29</v>
+        <v>81.8</v>
       </c>
       <c r="L6">
-        <v>0.8266331658291457</v>
+        <v>0.8270980788675429</v>
       </c>
       <c r="M6">
-        <v>0.637</v>
+        <v>-0</v>
       </c>
       <c r="N6">
-        <v>0.02578947368421053</v>
+        <v>-0</v>
       </c>
       <c r="O6">
-        <v>0.1936170212765957</v>
+        <v>-0</v>
       </c>
       <c r="P6">
-        <v>0.637</v>
+        <v>-0</v>
       </c>
       <c r="Q6">
-        <v>0.02578947368421053</v>
+        <v>-0</v>
       </c>
       <c r="R6">
-        <v>0.1936170212765957</v>
+        <v>-0</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
       <c r="U6">
-        <v>3.47</v>
+        <v>0.55</v>
       </c>
       <c r="V6">
-        <v>0.1404858299595142</v>
+        <v>0.00111970684039088</v>
       </c>
       <c r="W6">
-        <v>0.1170818505338078</v>
+        <v>0.1000978952520803</v>
       </c>
       <c r="X6">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="Y6">
-        <v>0.05966785662927667</v>
+        <v>0.006057552529888377</v>
       </c>
       <c r="Z6">
-        <v>0.147080561714708</v>
+        <v>0.1211787048949335</v>
       </c>
       <c r="AA6">
-        <v>0.1148800645031244</v>
+        <v>0.1002266740182564</v>
       </c>
       <c r="AB6">
-        <v>0.05741399390453115</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AC6">
-        <v>0.05746607059859322</v>
+        <v>0.006186331296064551</v>
       </c>
       <c r="AD6">
         <v>0</v>
@@ -1166,7 +1172,7 @@
         <v>0</v>
       </c>
       <c r="AG6">
-        <v>-3.47</v>
+        <v>-0.55</v>
       </c>
       <c r="AH6">
         <v>0</v>
@@ -1175,28 +1181,16 @@
         <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.1634479510127179</v>
+        <v>-0.001120961989198003</v>
       </c>
       <c r="AK6">
-        <v>-0.1364530082579631</v>
+        <v>-0.0006786353260534271</v>
       </c>
       <c r="AL6">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM6">
-        <v>0.001</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>3120</v>
-      </c>
-      <c r="AP6">
-        <v>-1.087774294670846</v>
-      </c>
-      <c r="AQ6">
-        <v>3120</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -1207,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>African Rainbow Capital Investments Limited (JSE:AIL)</t>
+          <t>The Mauritius Development Investment Trust Company Limited (MUSE:MDIT.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1215,6 +1209,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.227</v>
+      </c>
+      <c r="E7">
+        <v>-0.274</v>
+      </c>
       <c r="G7">
         <v>0</v>
       </c>
@@ -1222,94 +1222,103 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>0.9922480620155039</v>
+        <v>0.6835443037974683</v>
       </c>
       <c r="J7">
-        <v>0.9922480620155039</v>
+        <v>0.6789873417721518</v>
       </c>
       <c r="K7">
-        <v>64</v>
+        <v>1.04</v>
       </c>
       <c r="L7">
-        <v>0.9922480620155039</v>
+        <v>0.6582278481012658</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>1.3</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.05829596412556054</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>1.25</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>1.3</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.05829596412556054</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>1.25</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>1.05</v>
+        <v>0.874</v>
       </c>
       <c r="V7">
-        <v>0.001869991095280499</v>
+        <v>0.03919282511210762</v>
       </c>
       <c r="W7">
-        <v>0.1110147441457068</v>
+        <v>0.03151515151515152</v>
       </c>
       <c r="X7">
-        <v>0.05741399390453115</v>
+        <v>0.1008413454550967</v>
       </c>
       <c r="Y7">
-        <v>0.0536007502411757</v>
+        <v>-0.06932619393994521</v>
       </c>
       <c r="Z7">
-        <v>0.1120959332638165</v>
+        <v>0.04562122830826092</v>
       </c>
       <c r="AA7">
-        <v>0.1112269725408412</v>
+        <v>0.03097623653740652</v>
       </c>
       <c r="AB7">
-        <v>0.05741399390453115</v>
+        <v>0.09729844551838765</v>
       </c>
       <c r="AC7">
-        <v>0.05381297863631001</v>
+        <v>-0.06632220898098112</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="AG7">
-        <v>-1.05</v>
+        <v>2.356</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.1265178221699961</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.09633164330450343</v>
       </c>
       <c r="AJ7">
-        <v>-0.001873494513337496</v>
+        <v>0.09555483452303699</v>
       </c>
       <c r="AK7">
-        <v>-0.001286528211725786</v>
+        <v>0.07214600685938266</v>
       </c>
       <c r="AL7">
-        <v>0</v>
+        <v>0.041</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.041</v>
+      </c>
+      <c r="AO7">
+        <v>26.34146341463415</v>
+      </c>
+      <c r="AQ7">
+        <v>26.34146341463415</v>
       </c>
     </row>
     <row r="8">
@@ -1320,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EPE Capital Partners Ltd (JSE:EPE)</t>
+          <t>Promotion and Development Ltd (MUSE:PAD.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1328,107 +1337,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D8">
+        <v>0.0165</v>
+      </c>
+      <c r="E8">
+        <v>0.46</v>
+      </c>
       <c r="G8">
-        <v>0</v>
+        <v>0.1407407407407407</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>0.1407407407407407</v>
       </c>
       <c r="I8">
-        <v>0.7456140350877194</v>
+        <v>0.1185185185185185</v>
       </c>
       <c r="J8">
-        <v>0.3728070175438597</v>
+        <v>0.1117270079067832</v>
       </c>
       <c r="K8">
-        <v>0.325</v>
+        <v>15.6</v>
       </c>
       <c r="L8">
-        <v>0.1425438596491228</v>
+        <v>1.155555555555555</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>4.2401</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.04829271070615034</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.2718012820512821</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>4.2401</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.04829271070615034</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.2718012820512821</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>0.321</v>
+        <v>0.231</v>
       </c>
       <c r="V8">
-        <v>0.003933823529411765</v>
+        <v>0.002630979498861048</v>
       </c>
       <c r="W8">
-        <v>0.003292806484295846</v>
+        <v>0.05284552845528456</v>
       </c>
       <c r="X8">
-        <v>0.06221839529577479</v>
+        <v>0.1158061702446774</v>
       </c>
       <c r="Y8">
-        <v>-0.05892558881147894</v>
+        <v>-0.06296064178939287</v>
       </c>
       <c r="Z8">
-        <v>0.02092914383278715</v>
+        <v>0.04016327113480579</v>
       </c>
       <c r="AA8">
-        <v>0.007802531692047842</v>
+        <v>0.004487322111640724</v>
       </c>
       <c r="AB8">
-        <v>0.05884740240638023</v>
+        <v>0.1021968524149939</v>
       </c>
       <c r="AC8">
-        <v>-0.05104487071433238</v>
+        <v>-0.09770953030335316</v>
       </c>
       <c r="AD8">
-        <v>10.9</v>
+        <v>40.7</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>10.9</v>
+        <v>40.7</v>
       </c>
       <c r="AG8">
-        <v>10.579</v>
+        <v>40.469</v>
       </c>
       <c r="AH8">
-        <v>0.1178378378378378</v>
+        <v>0.3167315175097277</v>
       </c>
       <c r="AI8">
-        <v>0.08307926829268293</v>
+        <v>0.112152108018738</v>
       </c>
       <c r="AJ8">
-        <v>0.1147658360364074</v>
+        <v>0.3155010173931347</v>
       </c>
       <c r="AK8">
-        <v>0.08083038531773624</v>
+        <v>0.1115865982479892</v>
       </c>
       <c r="AL8">
-        <v>0.88</v>
+        <v>1.62</v>
       </c>
       <c r="AM8">
-        <v>0.88</v>
+        <v>1.62</v>
       </c>
       <c r="AO8">
-        <v>1.931818181818182</v>
+        <v>0.9876543209876543</v>
       </c>
       <c r="AQ8">
-        <v>1.931818181818182</v>
+        <v>0.9876543209876543</v>
       </c>
     </row>
     <row r="9">
@@ -1439,7 +1457,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Promotion and Development Ltd (MUSE:PAD.N0000)</t>
+          <t>Brait PLC (JSE:BAT)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1447,116 +1465,294 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D9">
-        <v>0.0123</v>
-      </c>
-      <c r="E9">
-        <v>-0.241</v>
-      </c>
       <c r="G9">
-        <v>0.1165467625899281</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>0.1165467625899281</v>
+        <v>0</v>
       </c>
       <c r="I9">
-        <v>0.1503597122302158</v>
+        <v>0.6372950819672131</v>
       </c>
       <c r="J9">
-        <v>0.1503597122302158</v>
+        <v>0.6372950819672131</v>
       </c>
       <c r="K9">
-        <v>5.25</v>
+        <v>-11.7</v>
       </c>
       <c r="L9">
-        <v>0.3776978417266187</v>
+        <v>-2.397540983606557</v>
       </c>
       <c r="M9">
-        <v>3.6566</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.04145804988662131</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.6964952380952381</v>
+        <v>0</v>
       </c>
       <c r="P9">
-        <v>3.6566</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.04145804988662131</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.6964952380952381</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>0.172</v>
+        <v>0.111</v>
       </c>
       <c r="V9">
-        <v>0.001950113378684807</v>
+        <v>0.0003712374581939799</v>
       </c>
       <c r="W9">
-        <v>0.01987130961392884</v>
+        <v>-0.01634991615427613</v>
       </c>
       <c r="X9">
-        <v>0.0741740775446082</v>
+        <v>0.1186481602769824</v>
       </c>
       <c r="Y9">
-        <v>-0.05430276793067935</v>
+        <v>-0.1349980764312585</v>
       </c>
       <c r="Z9">
-        <v>0.04486548424059519</v>
+        <v>0.004202730052103518</v>
       </c>
       <c r="AA9">
-        <v>0.006745961299485176</v>
+        <v>0.002678379193041381</v>
       </c>
       <c r="AB9">
-        <v>0.06128058732705664</v>
+        <v>0.1017849488630685</v>
       </c>
       <c r="AC9">
-        <v>-0.05453462602757146</v>
+        <v>-0.09910656967002708</v>
       </c>
       <c r="AD9">
-        <v>41.1</v>
+        <v>156.7</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>41.1</v>
+        <v>156.7</v>
       </c>
       <c r="AG9">
-        <v>40.928</v>
+        <v>156.589</v>
       </c>
       <c r="AH9">
-        <v>0.3178654292343387</v>
+        <v>0.3438665788896204</v>
       </c>
       <c r="AI9">
-        <v>0.1126953660542912</v>
+        <v>0.2029792746113989</v>
       </c>
       <c r="AJ9">
-        <v>0.3169568180410136</v>
+        <v>0.343706718116548</v>
       </c>
       <c r="AK9">
-        <v>0.1122766975376377</v>
+        <v>0.2028646605923909</v>
       </c>
       <c r="AL9">
-        <v>1.67</v>
+        <v>15</v>
       </c>
       <c r="AM9">
-        <v>1.67</v>
+        <v>15</v>
       </c>
       <c r="AO9">
-        <v>1.251497005988024</v>
+        <v>0.2073333333333333</v>
       </c>
       <c r="AQ9">
-        <v>1.251497005988024</v>
+        <v>0.2073333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tadvest Limited (NMSE:TAD)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K10">
+        <v>-6.41</v>
+      </c>
+      <c r="M10">
+        <v>-0</v>
+      </c>
+      <c r="N10">
+        <v>-0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>-0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+      <c r="S10">
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <v>0.366</v>
+      </c>
+      <c r="V10">
+        <v>0.008992628992628992</v>
+      </c>
+      <c r="W10">
+        <v>-0.09891975308641976</v>
+      </c>
+      <c r="X10">
+        <v>0.09404034272219189</v>
+      </c>
+      <c r="Y10">
+        <v>-0.1929600958086116</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+      <c r="AA10">
+        <v>-0.09695011108866897</v>
+      </c>
+      <c r="AB10">
+        <v>0.09404034272219189</v>
+      </c>
+      <c r="AC10">
+        <v>-0.1909904538108609</v>
+      </c>
+      <c r="AD10">
+        <v>0</v>
+      </c>
+      <c r="AE10">
+        <v>0</v>
+      </c>
+      <c r="AF10">
+        <v>0</v>
+      </c>
+      <c r="AG10">
+        <v>-0.366</v>
+      </c>
+      <c r="AH10">
+        <v>0</v>
+      </c>
+      <c r="AI10">
+        <v>0</v>
+      </c>
+      <c r="AJ10">
+        <v>-0.009074230178013586</v>
+      </c>
+      <c r="AK10">
+        <v>-0.006306647827135817</v>
+      </c>
+      <c r="AL10">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AM10">
+        <v>-0.09299999999999999</v>
+      </c>
+      <c r="AO10">
+        <v>-74.28571428571428</v>
+      </c>
+      <c r="AQ10">
+        <v>67.0967741935484</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Mauritius</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Go Life International Limited (MUSE:GOLI.N0000)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="K11">
+        <v>-0.078</v>
+      </c>
+      <c r="M11">
+        <v>-0</v>
+      </c>
+      <c r="N11">
+        <v>-0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>-0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0.09404034272219189</v>
+      </c>
+      <c r="AB11">
+        <v>0.09404034272219189</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>-0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>-0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/mauritius/mauritius_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/mauritius/mauritius_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0165</v>
+        <v>-0.10095</v>
       </c>
       <c r="E2">
-        <v>0.358</v>
+        <v>0.11</v>
       </c>
       <c r="G2">
-        <v>0.0581453634085213</v>
+        <v>0.03145018756942165</v>
       </c>
       <c r="H2">
-        <v>0.0581453634085213</v>
+        <v>0.03145018756942165</v>
       </c>
       <c r="I2">
-        <v>0.7575313283208021</v>
+        <v>0.7266655955067169</v>
       </c>
       <c r="J2">
-        <v>0.7514094983927589</v>
+        <v>0.7061185826446377</v>
       </c>
       <c r="K2">
-        <v>117.422</v>
+        <v>102.26</v>
       </c>
       <c r="L2">
-        <v>0.7357268170426066</v>
+        <v>0.7143705421699372</v>
       </c>
       <c r="M2">
-        <v>6.92048</v>
+        <v>16.4989</v>
       </c>
       <c r="N2">
-        <v>0.006494444444444445</v>
+        <v>0.02243191798887846</v>
       </c>
       <c r="O2">
-        <v>0.05893682614842194</v>
+        <v>0.1613426559749657</v>
       </c>
       <c r="P2">
-        <v>6.92048</v>
+        <v>4.2989</v>
       </c>
       <c r="Q2">
-        <v>0.006494444444444445</v>
+        <v>0.005844787970251934</v>
       </c>
       <c r="R2">
-        <v>0.05893682614842194</v>
+        <v>0.04203892039898298</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>12.2</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>0.7394432356096468</v>
       </c>
       <c r="U2">
-        <v>12.272</v>
+        <v>5.916</v>
       </c>
       <c r="V2">
-        <v>0.01151651651651652</v>
+        <v>0.008043398458212669</v>
       </c>
       <c r="W2">
-        <v>0.05284552845528456</v>
+        <v>0.04689092762487258</v>
       </c>
       <c r="X2">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y2">
-        <v>-0.04119481426690733</v>
+        <v>-0.03184463656449971</v>
       </c>
       <c r="Z2">
-        <v>0.06194322414481673</v>
+        <v>0.06507101822026694</v>
       </c>
       <c r="AA2">
-        <v>0.03097623653740652</v>
+        <v>0.01236760253454145</v>
       </c>
       <c r="AB2">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC2">
-        <v>-0.06632220898098112</v>
+        <v>-0.07256922507605543</v>
       </c>
       <c r="AD2">
-        <v>228.73</v>
+        <v>242</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>228.73</v>
+        <v>242</v>
       </c>
       <c r="AG2">
-        <v>216.458</v>
+        <v>236.084</v>
       </c>
       <c r="AH2">
-        <v>0.1767169114522572</v>
+        <v>0.2475677998179047</v>
       </c>
       <c r="AI2">
-        <v>0.1021267893843147</v>
+        <v>0.1141563819785754</v>
       </c>
       <c r="AJ2">
-        <v>0.1688363552974982</v>
+        <v>0.2429862679267266</v>
       </c>
       <c r="AK2">
-        <v>0.09717988951218801</v>
+        <v>0.1116773408300824</v>
       </c>
       <c r="AL2">
-        <v>18.275</v>
+        <v>21.87</v>
       </c>
       <c r="AM2">
-        <v>18.098</v>
+        <v>21.837</v>
       </c>
       <c r="AN2">
-        <v>29.7051948051948</v>
+        <v>3781.25</v>
       </c>
       <c r="AO2">
-        <v>6.615704514363886</v>
+        <v>4.75628715134888</v>
       </c>
       <c r="AP2">
-        <v>28.11142857142857</v>
+        <v>3688.8125</v>
       </c>
       <c r="AQ2">
-        <v>6.680406674770693</v>
+        <v>4.763474836287037</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Investment Trust Ltd (MUSE:NITL.N0000)</t>
+          <t>African Rainbow Capital Investments Limited (JSE:AIL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,79 +722,76 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.522</v>
+        <v>0.216</v>
       </c>
       <c r="E3">
-        <v>0.736</v>
+        <v>0.241</v>
       </c>
       <c r="G3">
-        <v>0.9329962073324904</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.9329962073324904</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9683944374209861</v>
+        <v>0.9385574354407837</v>
       </c>
       <c r="J3">
-        <v>0.9683944374209861</v>
+        <v>0.9385574354407837</v>
       </c>
       <c r="K3">
-        <v>7.18</v>
+        <v>105.4</v>
       </c>
       <c r="L3">
-        <v>0.9077117572692793</v>
+        <v>0.9385574354407837</v>
       </c>
       <c r="M3">
-        <v>0.419</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.02193717277486911</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.05835654596100279</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>0.419</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.02193717277486911</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.05835654596100279</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>4.13</v>
+        <v>1.11</v>
       </c>
       <c r="V3">
-        <v>0.2162303664921466</v>
+        <v>0.003087621696801113</v>
       </c>
       <c r="W3">
-        <v>0.2484429065743945</v>
+        <v>0.1299630086313194</v>
       </c>
       <c r="X3">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y3">
-        <v>0.1544025638522026</v>
+        <v>0.05122744444194709</v>
       </c>
       <c r="Z3">
-        <v>0.3110499410145497</v>
+        <v>0.1385649947559997</v>
       </c>
       <c r="AA3">
-        <v>0.3012190326386158</v>
+        <v>0.1300512061200567</v>
       </c>
       <c r="AB3">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC3">
-        <v>0.2071786899164239</v>
+        <v>0.05131564193068446</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-4.13</v>
+        <v>-1.11</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,22 +812,16 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.2758851035404141</v>
+        <v>-0.003097184631267614</v>
       </c>
       <c r="AK3">
-        <v>-0.1737484223811527</v>
+        <v>-0.001360977942348484</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
         <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AP3">
-        <v>-0.5363636363636364</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EPE Capital Partners Ltd (JSE:EPE)</t>
+          <t>Tadvest Limited (NMSE:TAD)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,10 +841,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.31</v>
+        <v>0.0968</v>
       </c>
       <c r="E4">
-        <v>0.358</v>
+        <v>0.11</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -862,16 +853,16 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>0.9839743589743589</v>
+        <v>0.9589235127478754</v>
       </c>
       <c r="J4">
-        <v>0.9776415136190223</v>
+        <v>0.9507203322553419</v>
       </c>
       <c r="K4">
-        <v>28.7</v>
+        <v>6.72</v>
       </c>
       <c r="L4">
-        <v>0.9198717948717948</v>
+        <v>0.9518413597733711</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -895,67 +886,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.19</v>
+        <v>0.366</v>
       </c>
       <c r="V4">
-        <v>0.002219626168224299</v>
+        <v>0.008883495145631068</v>
       </c>
       <c r="W4">
-        <v>0.2385702410640066</v>
+        <v>0.1150684931506849</v>
       </c>
       <c r="X4">
-        <v>0.1094540762025605</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y4">
-        <v>0.1291161648614461</v>
+        <v>0.03633292896131264</v>
       </c>
       <c r="Z4">
-        <v>0.2383881294936545</v>
+        <v>0.1216528242064996</v>
       </c>
       <c r="AA4">
-        <v>0.2330581317469838</v>
+        <v>0.115657813449404</v>
       </c>
       <c r="AB4">
-        <v>0.09798895501806384</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC4">
-        <v>0.13506917672892</v>
+        <v>0.03692224926003174</v>
       </c>
       <c r="AD4">
-        <v>28.1</v>
+        <v>0</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>28.1</v>
+        <v>0</v>
       </c>
       <c r="AG4">
-        <v>27.91</v>
+        <v>-0.366</v>
       </c>
       <c r="AH4">
-        <v>0.247141600703606</v>
+        <v>0</v>
       </c>
       <c r="AI4">
-        <v>0.173778602350031</v>
+        <v>0</v>
       </c>
       <c r="AJ4">
-        <v>0.2458814201391948</v>
+        <v>-0.008963118969486211</v>
       </c>
       <c r="AK4">
-        <v>0.1728066373599158</v>
+        <v>-0.00565390675688201</v>
       </c>
       <c r="AL4">
-        <v>1.53</v>
+        <v>0.01</v>
       </c>
       <c r="AM4">
-        <v>1.53</v>
+        <v>-0.023</v>
       </c>
       <c r="AO4">
-        <v>20.06535947712418</v>
+        <v>677</v>
       </c>
       <c r="AQ4">
-        <v>20.06535947712418</v>
+        <v>-294.3478260869565</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +957,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Bee Equity Partners Ltd (MUSE:FIDE.I0000)</t>
+          <t>The Mauritius Development Investment Trust Company Limited (MUSE:MDIT.N0000)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,10 +966,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0629</v>
+        <v>-0.239</v>
       </c>
       <c r="E5">
-        <v>-0.0071</v>
+        <v>-0.29</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -987,67 +978,64 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>0.7791411042944786</v>
+        <v>0.6526315789473685</v>
       </c>
       <c r="J5">
-        <v>0.7773291482379797</v>
+        <v>0.6526315789473685</v>
       </c>
       <c r="K5">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="L5">
-        <v>0.7914110429447854</v>
+        <v>0.6578947368421053</v>
       </c>
       <c r="M5">
-        <v>0.96138</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.0882</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.7452558139534884</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>0.96138</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.0882</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.7452558139534884</v>
+        <v>-0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
       <c r="U5">
-        <v>5.82</v>
+        <v>0.589</v>
       </c>
       <c r="V5">
-        <v>0.5339449541284403</v>
+        <v>0.03116402116402116</v>
       </c>
       <c r="W5">
-        <v>0.09923076923076923</v>
+        <v>0.04125412541254125</v>
       </c>
       <c r="X5">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y5">
-        <v>0.005190426508577345</v>
+        <v>-0.03748143877683104</v>
       </c>
       <c r="Z5">
-        <v>0.2084398976982097</v>
+        <v>0.05818226359627633</v>
       </c>
       <c r="AA5">
-        <v>0.162026408136561</v>
+        <v>0.03797158255756982</v>
       </c>
       <c r="AB5">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC5">
-        <v>0.06798606541436908</v>
+        <v>-0.04076398163180247</v>
       </c>
       <c r="AD5">
         <v>0</v>
@@ -1059,7 +1047,7 @@
         <v>0</v>
       </c>
       <c r="AG5">
-        <v>-5.82</v>
+        <v>-0.589</v>
       </c>
       <c r="AH5">
         <v>0</v>
@@ -1068,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-1.145669291338583</v>
+        <v>-0.03216645732073617</v>
       </c>
       <c r="AK5">
-        <v>-0.8584070796460178</v>
+        <v>-0.01887155169651725</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1088,7 +1076,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>African Rainbow Capital Investments Limited (JSE:AIL)</t>
+          <t>EPE Capital Partners Ltd (JSE:EPE)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1096,6 +1084,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.07190000000000001</v>
+      </c>
+      <c r="E6">
+        <v>-0.431</v>
+      </c>
       <c r="G6">
         <v>0</v>
       </c>
@@ -1103,25 +1097,25 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0.8270980788675429</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="J6">
-        <v>0.8270980788675429</v>
+        <v>0.6719101123595506</v>
       </c>
       <c r="K6">
-        <v>81.8</v>
+        <v>0.276</v>
       </c>
       <c r="L6">
-        <v>0.8270980788675429</v>
+        <v>0.07360000000000001</v>
       </c>
       <c r="M6">
-        <v>-0</v>
+        <v>1.06</v>
       </c>
       <c r="N6">
-        <v>-0</v>
+        <v>0.01591591591591592</v>
       </c>
       <c r="O6">
-        <v>-0</v>
+        <v>3.840579710144927</v>
       </c>
       <c r="P6">
         <v>-0</v>
@@ -1133,64 +1127,73 @@
         <v>-0</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.06</v>
+      </c>
+      <c r="T6">
+        <v>1</v>
       </c>
       <c r="U6">
-        <v>0.55</v>
+        <v>0.597</v>
       </c>
       <c r="V6">
-        <v>0.00111970684039088</v>
+        <v>0.008963963963963964</v>
       </c>
       <c r="W6">
-        <v>0.1000978952520803</v>
+        <v>0.002065868263473054</v>
       </c>
       <c r="X6">
-        <v>0.09404034272219189</v>
+        <v>0.09300683187266148</v>
       </c>
       <c r="Y6">
-        <v>0.006057552529888377</v>
+        <v>-0.09094096360918844</v>
       </c>
       <c r="Z6">
-        <v>0.1211787048949335</v>
+        <v>0.02321837657111015</v>
       </c>
       <c r="AA6">
-        <v>0.1002266740182564</v>
+        <v>0.01560066201070098</v>
       </c>
       <c r="AB6">
-        <v>0.09404034272219189</v>
+        <v>0.08283460914247474</v>
       </c>
       <c r="AC6">
-        <v>0.006186331296064551</v>
+        <v>-0.06723394713177376</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG6">
-        <v>-0.55</v>
+        <v>27.403</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.2959830866807611</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.1953942777390091</v>
       </c>
       <c r="AJ6">
-        <v>-0.001120961989198003</v>
+        <v>0.2915119730221376</v>
       </c>
       <c r="AK6">
-        <v>-0.0006786353260534271</v>
+        <v>0.1920281984261017</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>2.82</v>
+      </c>
+      <c r="AO6">
+        <v>1.152482269503546</v>
+      </c>
+      <c r="AQ6">
+        <v>1.152482269503546</v>
       </c>
     </row>
     <row r="7">
@@ -1201,7 +1204,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Mauritius Development Investment Trust Company Limited (MUSE:MDIT.N0000)</t>
+          <t>Promotion and Development Ltd (MUSE:PAD.N0000)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1210,46 +1213,43 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.227</v>
-      </c>
-      <c r="E7">
-        <v>-0.274</v>
+        <v>0.06559999999999999</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>0.235632183908046</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>0.235632183908046</v>
       </c>
       <c r="I7">
-        <v>0.6835443037974683</v>
+        <v>0.2431034482758621</v>
       </c>
       <c r="J7">
-        <v>0.6789873417721518</v>
+        <v>0.2379476972922935</v>
       </c>
       <c r="K7">
-        <v>1.04</v>
+        <v>13.8</v>
       </c>
       <c r="L7">
-        <v>0.6582278481012658</v>
+        <v>0.7931034482758622</v>
       </c>
       <c r="M7">
-        <v>1.3</v>
+        <v>3.9289</v>
       </c>
       <c r="N7">
-        <v>0.05829596412556054</v>
+        <v>0.04384933035714286</v>
       </c>
       <c r="O7">
-        <v>1.25</v>
+        <v>0.2847028985507246</v>
       </c>
       <c r="P7">
-        <v>1.3</v>
+        <v>3.9289</v>
       </c>
       <c r="Q7">
-        <v>0.05829596412556054</v>
+        <v>0.04384933035714286</v>
       </c>
       <c r="R7">
-        <v>1.25</v>
+        <v>0.2847028985507246</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1258,67 +1258,67 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>0.874</v>
+        <v>0.406</v>
       </c>
       <c r="V7">
-        <v>0.03919282511210762</v>
+        <v>0.004531250000000001</v>
       </c>
       <c r="W7">
-        <v>0.03151515151515152</v>
+        <v>0.04689092762487258</v>
       </c>
       <c r="X7">
-        <v>0.1008413454550967</v>
+        <v>0.09290466670700784</v>
       </c>
       <c r="Y7">
-        <v>-0.06932619393994521</v>
+        <v>-0.04601373908213526</v>
       </c>
       <c r="Z7">
-        <v>0.04562122830826092</v>
+        <v>0.05197613877031624</v>
       </c>
       <c r="AA7">
-        <v>0.03097623653740652</v>
+        <v>0.01236760253454145</v>
       </c>
       <c r="AB7">
-        <v>0.09729844551838765</v>
+        <v>0.08493682761059687</v>
       </c>
       <c r="AC7">
-        <v>-0.06632220898098112</v>
+        <v>-0.07256922507605543</v>
       </c>
       <c r="AD7">
-        <v>3.23</v>
+        <v>37.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3.23</v>
+        <v>37.4</v>
       </c>
       <c r="AG7">
-        <v>2.356</v>
+        <v>36.994</v>
       </c>
       <c r="AH7">
-        <v>0.1265178221699961</v>
+        <v>0.294488188976378</v>
       </c>
       <c r="AI7">
-        <v>0.09633164330450343</v>
+        <v>0.09795704557359874</v>
       </c>
       <c r="AJ7">
-        <v>0.09555483452303699</v>
+        <v>0.2922255399150039</v>
       </c>
       <c r="AK7">
-        <v>0.07214600685938266</v>
+        <v>0.09699680645212037</v>
       </c>
       <c r="AL7">
-        <v>0.041</v>
+        <v>2.64</v>
       </c>
       <c r="AM7">
-        <v>0.041</v>
+        <v>2.64</v>
       </c>
       <c r="AO7">
-        <v>26.34146341463415</v>
+        <v>1.602272727272727</v>
       </c>
       <c r="AQ7">
-        <v>26.34146341463415</v>
+        <v>1.602272727272727</v>
       </c>
     </row>
     <row r="8">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Promotion and Development Ltd (MUSE:PAD.N0000)</t>
+          <t>National Investment Trust Ltd (MUSE:NITL.N0000)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1338,115 +1338,112 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0165</v>
-      </c>
-      <c r="E8">
-        <v>0.46</v>
+        <v>-0.13</v>
       </c>
       <c r="G8">
-        <v>0.1407407407407407</v>
+        <v>0.7256317689530686</v>
       </c>
       <c r="H8">
-        <v>0.1407407407407407</v>
+        <v>0.7256317689530686</v>
       </c>
       <c r="I8">
-        <v>0.1185185185185185</v>
+        <v>0.05776173285198555</v>
       </c>
       <c r="J8">
-        <v>0.1117270079067832</v>
+        <v>0.05776173285198555</v>
       </c>
       <c r="K8">
-        <v>15.6</v>
+        <v>-0.166</v>
       </c>
       <c r="L8">
-        <v>1.155555555555555</v>
+        <v>-0.2996389891696751</v>
       </c>
       <c r="M8">
-        <v>4.2401</v>
+        <v>4.75</v>
       </c>
       <c r="N8">
-        <v>0.04829271070615034</v>
+        <v>0.4439252336448599</v>
       </c>
       <c r="O8">
-        <v>0.2718012820512821</v>
+        <v>-28.6144578313253</v>
       </c>
       <c r="P8">
-        <v>4.2401</v>
+        <v>0.37</v>
       </c>
       <c r="Q8">
-        <v>0.04829271070615034</v>
+        <v>0.03457943925233645</v>
       </c>
       <c r="R8">
-        <v>0.2718012820512821</v>
+        <v>-2.228915662650602</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>4.38</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.9221052631578948</v>
       </c>
       <c r="U8">
-        <v>0.231</v>
+        <v>0.862</v>
       </c>
       <c r="V8">
-        <v>0.002630979498861048</v>
+        <v>0.08056074766355141</v>
       </c>
       <c r="W8">
-        <v>0.05284552845528456</v>
+        <v>-0.005949820788530466</v>
       </c>
       <c r="X8">
-        <v>0.1158061702446774</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y8">
-        <v>-0.06296064178939287</v>
+        <v>-0.08468538497790276</v>
       </c>
       <c r="Z8">
-        <v>0.04016327113480579</v>
+        <v>0.0233066891039125</v>
       </c>
       <c r="AA8">
-        <v>0.004487322111640724</v>
+        <v>0.001346234749684476</v>
       </c>
       <c r="AB8">
-        <v>0.1021968524149939</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC8">
-        <v>-0.09770953030335316</v>
+        <v>-0.07738932943968781</v>
       </c>
       <c r="AD8">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>40.7</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>40.469</v>
+        <v>-0.862</v>
       </c>
       <c r="AH8">
-        <v>0.3167315175097277</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.112152108018738</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>0.3155010173931347</v>
+        <v>-0.08761943484448059</v>
       </c>
       <c r="AK8">
-        <v>0.1115865982479892</v>
+        <v>-0.03841697120955521</v>
       </c>
       <c r="AL8">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>1.62</v>
-      </c>
-      <c r="AO8">
-        <v>0.9876543209876543</v>
-      </c>
-      <c r="AQ8">
-        <v>0.9876543209876543</v>
+        <v>0</v>
+      </c>
+      <c r="AN8">
+        <v>0</v>
+      </c>
+      <c r="AP8">
+        <v>-13.46875</v>
       </c>
     </row>
     <row r="9">
@@ -1457,7 +1454,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Brait PLC (JSE:BAT)</t>
+          <t>The Bee Equity Partners Ltd (MUSE:FIDE.I0000)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1465,6 +1462,12 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D9">
+        <v>-0.427</v>
+      </c>
+      <c r="E9">
+        <v>0.129</v>
+      </c>
       <c r="G9">
         <v>0</v>
       </c>
@@ -1472,16 +1475,16 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>0.6372950819672131</v>
+        <v>-0.485207100591716</v>
       </c>
       <c r="J9">
-        <v>0.6372950819672131</v>
+        <v>-0.485207100591716</v>
       </c>
       <c r="K9">
-        <v>-11.7</v>
+        <v>1.2</v>
       </c>
       <c r="L9">
-        <v>-2.397540983606557</v>
+        <v>7.10059171597633</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1490,7 +1493,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1499,73 +1502,67 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>0.111</v>
+        <v>1.88</v>
       </c>
       <c r="V9">
-        <v>0.0003712374581939799</v>
+        <v>0.4934383202099737</v>
       </c>
       <c r="W9">
-        <v>-0.01634991615427613</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="X9">
-        <v>0.1186481602769824</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y9">
-        <v>-0.1349980764312585</v>
+        <v>0.01650253104872294</v>
       </c>
       <c r="Z9">
-        <v>0.004202730052103518</v>
+        <v>0.02492625368731564</v>
       </c>
       <c r="AA9">
-        <v>0.002678379193041381</v>
+        <v>-0.01209439528023599</v>
       </c>
       <c r="AB9">
-        <v>0.1017849488630685</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC9">
-        <v>-0.09910656967002708</v>
+        <v>-0.09082995946960828</v>
       </c>
       <c r="AD9">
-        <v>156.7</v>
+        <v>0</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>156.7</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>156.589</v>
+        <v>-1.88</v>
       </c>
       <c r="AH9">
-        <v>0.3438665788896204</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>0.2029792746113989</v>
+        <v>0</v>
       </c>
       <c r="AJ9">
-        <v>0.343706718116548</v>
+        <v>-0.9740932642487046</v>
       </c>
       <c r="AK9">
-        <v>0.2028646605923909</v>
+        <v>-1.392592592592592</v>
       </c>
       <c r="AL9">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AM9">
-        <v>15</v>
-      </c>
-      <c r="AO9">
-        <v>0.2073333333333333</v>
-      </c>
-      <c r="AQ9">
-        <v>0.2073333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1576,7 +1573,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tadvest Limited (NMSE:TAD)</t>
+          <t>Brait PLC (JSE:BAT)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1585,7 +1582,7 @@
         </is>
       </c>
       <c r="K10">
-        <v>-6.41</v>
+        <v>-26.1</v>
       </c>
       <c r="M10">
         <v>-0</v>
@@ -1609,67 +1606,67 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0.366</v>
+        <v>0.106</v>
       </c>
       <c r="V10">
-        <v>0.008992628992628992</v>
+        <v>0.0008066971080669711</v>
       </c>
       <c r="W10">
-        <v>-0.09891975308641976</v>
+        <v>-0.04241833252072161</v>
       </c>
       <c r="X10">
-        <v>0.09404034272219189</v>
+        <v>0.1243575393831826</v>
       </c>
       <c r="Y10">
-        <v>-0.1929600958086116</v>
+        <v>-0.1667758719039042</v>
       </c>
       <c r="Z10">
         <v>0</v>
       </c>
       <c r="AA10">
-        <v>-0.09695011108866897</v>
+        <v>-0.02163523511800272</v>
       </c>
       <c r="AB10">
-        <v>0.09404034272219189</v>
+        <v>0.0866762089763288</v>
       </c>
       <c r="AC10">
-        <v>-0.1909904538108609</v>
+        <v>-0.1083114440943315</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>176.6</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>176.6</v>
       </c>
       <c r="AG10">
-        <v>-0.366</v>
+        <v>176.494</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.5733766233766233</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.2696594899984731</v>
       </c>
       <c r="AJ10">
-        <v>-0.009074230178013586</v>
+        <v>0.5732297479002514</v>
       </c>
       <c r="AK10">
-        <v>-0.006306647827135817</v>
+        <v>0.2695412603047676</v>
       </c>
       <c r="AL10">
-        <v>0.08400000000000001</v>
+        <v>16.4</v>
       </c>
       <c r="AM10">
-        <v>-0.09299999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="AO10">
-        <v>-74.28571428571428</v>
+        <v>-1.018292682926829</v>
       </c>
       <c r="AQ10">
-        <v>67.0967741935484</v>
+        <v>-1.018292682926829</v>
       </c>
     </row>
     <row r="11">
@@ -1680,7 +1677,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Go Life International Limited (MUSE:GOLI.N0000)</t>
+          <t>Numeral Limited (MUSE:GOLI.N0000)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1688,17 +1685,35 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D11">
+        <v>-0.654</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>-8.571428571428571</v>
+      </c>
+      <c r="J11">
+        <v>-8.571428571428571</v>
+      </c>
       <c r="K11">
-        <v>-0.078</v>
+        <v>-0.12</v>
+      </c>
+      <c r="L11">
+        <v>-8.571428571428571</v>
       </c>
       <c r="M11">
-        <v>-0</v>
+        <v>6.76</v>
       </c>
       <c r="N11">
-        <v>-0</v>
+        <v>0.4898550724637681</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>-56.33333333333334</v>
       </c>
       <c r="P11">
         <v>-0</v>
@@ -1710,7 +1725,10 @@
         <v>0</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>6.76</v>
+      </c>
+      <c r="T11">
+        <v>1</v>
       </c>
       <c r="U11">
         <v>0</v>
@@ -1718,11 +1736,17 @@
       <c r="V11">
         <v>0</v>
       </c>
+      <c r="W11">
+        <v>0.3305785123966942</v>
+      </c>
       <c r="X11">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
+      </c>
+      <c r="Y11">
+        <v>0.2518429482073219</v>
       </c>
       <c r="AB11">
-        <v>0.09404034272219189</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AD11">
         <v>0</v>
